--- a/PFE/NEW/PFE_metadata_addin.xlsx
+++ b/PFE/NEW/PFE_metadata_addin.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="662">
   <si>
     <t xml:space="preserve">PFE Metadata — Line / Scenario / Deal Facts (add-in tabs for metadata_workbook_consolidated_v2)</t>
   </si>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">• HC materiality: 712 traded HC lines carry ~84.4bn (41% of portfolio); 675 no-deal HC lines are immaterial.</t>
   </si>
   <si>
-    <t xml:space="preserve">• CP/HC meaning (HC=agent/fund/house facility, CP=legal counterparty) is a WORKING HYPOTHESIS pending data-owner confirmation.</t>
+    <t xml:space="preserve">• CP/HC meaning (HC=Holding Company facility, CP=legal counterparty) is a WORKING HYPOTHESIS pending data-owner confirmation.</t>
   </si>
   <si>
     <t xml:space="preserve">Object name (FQN)</t>
@@ -183,7 +183,7 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">CONFORMED DIMENSION (counterparty). Home of DEEP counterparty detail: full ratings set (td/s&amp;p/moody/composite), agreements (ISDA/CSA/IFEMA), netting flags, parent hierarchy. Facts reach it via counterparty key. Common slicers (industry/sector/country) are denormalized onto the line fact for speed; this dim holds the authoritative + deep attributes. Counterparty dimension: deep detail (td_account_rating, s&amp;p/moody/composite, ISDA/CSA/IFEMA, netting, SIC hierarchy, parent hierarchy). PK counterparty_code. counterparty_code = the Line value in ats_summary/asts (the CP-to-line link is this equality, NOT c2c_line/cont_line). Physically replicated per source(scenario) x business_date — take one slice (source=CARTOR, one date) for a 1-row-per-counterparty dimension.</t>
+    <t xml:space="preserve">CONFORMED DIMENSION (counterparty). Home of DEEP counterparty detail: full ratings set (td/s&amp;p/moody/composite), agreements (ISDA/CSA/IFEMA), netting flags, parent hierarchy. Facts reach it via counterparty key. Common slicers (industry/sector/country) are denormalized onto the line fact for speed; this dim holds the authoritative + deep attributes. Counterparty dimension: deep detail (td_account_rating, s&amp;p/moody/composite, ISDA/CSA/IFEMA, netting, SIC hierarchy, parent hierarchy). PK counterparty_code. counterparty_code = the Line value in ats_summary/asts (the CP-to-line link is this equality, NOT c2c_line/cont_line). Physically replicated per source(scenario) x business_date — take one slice (source=CARTOR, one date) for a 1-row-per-counterparty dimension. | HIERARCHY (data-owner confirmed): counterparty_code (CP, leaf) -&gt; immediate_parent (HC=Holding Company) -&gt; ultimate_parent (UP). HC lines map to their counterparty family via immediate_parent (all 1,387 resolve). HC exposure INDEPENDENT of children (not a roll-up) -&gt; CP+HC additive. Source of vw_dim_client (sliced source=CARTOR + MAX(business_date), one row per counterparty).</t>
   </si>
   <si>
     <t xml:space="preserve">d4001-centralus-tdvip-creditrisk.xvala_core.pfe_ats_summary</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Line-grain scenario SUMMARY: the 8 scenario maxima as columns, max_of_all, scenario_of_max, plus dims (sic/industry/brr/otc) and limits.</t>
   </si>
   <si>
-    <t xml:space="preserve">Line spine. 8 scenario maxima as COLUMNS (cartor_max..strmpr025_max), max_of_all=GREATEST of 8, scenario_of_max. Denormalized CP reference attrs (sic_industry, industry, sic_code, country, region, otc_sft) + worst_rating_of_associated_clients (brr). Folded inline into vw_pfe_ats_lines_detail as the ats_clean CTE. KEY: line IS the counterparty_code in pfe_clients_report (same identifier) — FK line -&gt; pfe_clients_report.counterparty_code. 10,417/11,804 match; 1,387 have no counterparty_code in clients_report (anomaly). | LINE FORMAT SPLIT: 10,417 CP_ lines (= counterparty_code, join CP dim directly) + 1,387 HC_ lines (different format; NOT in clients_report as a code). HC = likely agent/fund/house-level facility (hypothesis, pending data-owner confirm); posts to a CP only when it trades. Of the 1,387 HC: 712 have deals &amp; carry ~all HC exposure (~84.4bn, resolve to CP via deal crosswalk); 675 have no deals &amp; are effectively empty (only 3 with any PFE).</t>
+    <t xml:space="preserve">Line spine. 8 scenario maxima as COLUMNS (cartor_max..strmpr025_max), max_of_all=GREATEST of 8, scenario_of_max. Denormalized CP reference attrs (sic_industry, industry, sic_code, country, region, otc_sft) + worst_rating_of_associated_clients (brr). Folded inline into vw_pfe_ats_lines_detail as the ats_clean CTE. KEY: line IS the counterparty_code in pfe_clients_report (same identifier) — FK line -&gt; pfe_clients_report.counterparty_code. 10,417/11,804 match; 1,387 have no counterparty_code in clients_report (anomaly). | LINE FORMAT SPLIT: 10,417 CP_ lines (= counterparty_code, join CP dim directly) + 1,387 HC_ lines (different format; NOT in clients_report as a code). HC = likely Holding Company-level facility (hypothesis, pending data-owner confirm); posts to a CP only when it trades. Of the 1,387 HC: 712 have deals &amp; carry ~all HC exposure (~84.4bn, resolve to CP via deal crosswalk); 675 have no deals &amp; are effectively empty (only 3 with any PFE).</t>
   </si>
   <si>
     <t xml:space="preserve">d4001-centralus-tdvip-creditrisk.xvala_core.pfe_asts</t>
@@ -339,7 +339,7 @@
     <t xml:space="preserve">The DEAL FACT: trade-level detail with each deal's line context (breach, utilization, limit) stapled on for drill-down.</t>
   </si>
   <si>
-    <t xml:space="preserve">Base = pfe_deals_report; LEFT JOIN vw_pfe_line_detail on trim(upper(Line)). Line context repeated per deal (do-not-sum). Window aggregates full-precision (no ROUND on summed fractions).</t>
+    <t xml:space="preserve">Base = pfe_deals_report; LEFT JOIN vw_pfe_line_detail on trim(upper(Line)). Line context repeated per deal (do-not-sum). Window aggregates full-precision (no ROUND on summed fractions). | CHANGE: the LEFT JOIN to vw_pfe_ats_lines_detail was REMOVED — the deal fact no longer pre-joins line context (10 Line_* columns dropped). Line context now resolves via the Mosaic relationship deal.Line -&gt; line-fact.Line. View stands alone: deal attributes + conformed keys Line (exposure drill) and Counterparty_Code (CP attribution).</t>
   </si>
   <si>
     <t xml:space="preserve">d4001-centralus-tdvip-creditrisk.xvala_core.vw_ast_breach_report</t>
@@ -402,6 +402,30 @@
     <t xml:space="preserve">SCENARIO FACT. Unpivots pfe_ats_summary's 8 *_max columns into 8 scenario rows (friendly names). Scenario_Name=selectable attribute, Scenario_Exposure=measure. Ties to line fact's Line_Scn_* by construction. Line dims repeated per scenario row for standalone filtering. FK: Line -&gt; pfe_clients_report.counterparty_code (same as line fact).</t>
   </si>
   <si>
+    <t xml:space="preserve">d4001-centralus-tdvip-creditrisk.xvala_core.vw_dim_client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">one row per counterparty_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counterparty_Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE client/counterparty dimension. Created FROM pfe_clients_report, sliced to source=CARTOR + MAX(business_date) (reference data — current state; attributes stable across sources, verified 0 varying). Self-sufficient: model references this view, never raw clients_report. Carries CP-&gt;HC-&gt;UP hierarchy columns (immediate_parent/ultimate_parent) for the deferred parent view. Counterparty_Name searchable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4001-centralus-tdvip-creditrisk.xvala_core.vw_dim_scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario dimension (converted from table to VIEW; emits 8 rows via UNION ALL). Columns renamed: Scenario_Name, Source_Column_ATS, Source_Label_ASTS, Source_Label_LinesReport, Scenario_Type, Scenario_Order, Mapping_Confirmed.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Object</t>
   </si>
   <si>
@@ -897,9 +921,6 @@
     <t xml:space="preserve">pfe_asts</t>
   </si>
   <si>
-    <t xml:space="preserve">Scenario_Name</t>
-  </si>
-  <si>
     <t xml:space="preserve">Scenario display name.</t>
   </si>
   <si>
@@ -942,7 +963,7 @@
     <t xml:space="preserve">Counterparty identifier.</t>
   </si>
   <si>
-    <t xml:space="preserve">PK of the Counterparty dimension. The conformed key facts use to reach deep CP attributes (ratings set, agreements, netting, parent hierarchy).</t>
+    <t xml:space="preserve">PK of the Counterparty dimension. The conformed key facts use to reach deep CP attributes (ratings set, agreements, netting, parent hierarchy). | HIERARCHY: this is the CP leaf of a 3-level hierarchy counterparty_code (CP) -&gt; immediate_parent (HC=Holding Company) -&gt; ultimate_parent (UP). CP-format code; = the CP-format Line in ats_summary/asts.</t>
   </si>
   <si>
     <t xml:space="preserve">Line_IM</t>
@@ -1060,6 +1081,48 @@
   </si>
   <si>
     <t xml:space="preserve">Normalized. Repeated line attribute.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immediate_parent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding company this counterparty rolls up to (HC-format).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC = Holding Company (data-owner confirmed). The HC-LEVEL KEY: HC lines in the facts map to their counterparty family via immediate_parent (all 1,387 HC lines resolve). HC exposure is INDEPENDENT of its children (not a roll-up; verified) -&gt; CP+HC additive, no double-count. In v1 carried on vw_dim_client but NOT wired as a join path (HC drill uses the deal fact); the immediate_parent hierarchy is the DEFERRED secondary parent view.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hierarchy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pfe_clients_report.counterparty_code (self-ref parent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y (data owner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ultimate_parent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultimate parent (top of the corporate hierarchy, UP-format).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top level of counterparty_code -&gt; immediate_parent (HC) -&gt; ultimate_parent (UP). Carried on vw_dim_client for the deferred parent roll-up view.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">counterparty_long_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counterparty long name. SEARCHABLE (users search by name).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEARCHABLE display attribute in the model (users search by name, not just code). NOT a join key — one long name can map to several counterparty_codes; joins stay on the codes. Tracks counterparty_code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attribute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">none</t>
   </si>
   <si>
     <t xml:space="preserve">Friendly name</t>
@@ -1444,7 +1507,7 @@
     <t xml:space="preserve">10,417 CP · 1,387 HC.</t>
   </si>
   <si>
-    <t xml:space="preserve">ROOT CAUSE: ats_summary carries TWO line-key formats. CP_ lines (10,417) ARE counterparty_codes -&gt; join CP dimension directly on Line=counterparty_code. HC_ lines (1,387) are a DIFFERENT format that does not exist in clients_report as counterparty_code — this IS the 1,387 gap. WORKING HYPOTHESIS (pending data-owner confirmation): HC = agent/fund/house-level facility; CP = legal counterparty; a position posts to a CP only when the HC line trades.</t>
+    <t xml:space="preserve">ROOT CAUSE: ats_summary carries TWO line-key formats. CP_ lines (10,417) ARE counterparty_codes -&gt; join CP dimension directly on Line=counterparty_code. HC_ lines (1,387) are a DIFFERENT format that does not exist in clients_report as counterparty_code — this IS the 1,387 gap. WORKING HYPOTHESIS (pending data-owner confirmation): HC = Holding Company-level facility; CP = legal counterparty; a position posts to a CP only when the HC line trades.</t>
   </si>
   <si>
     <t xml:space="preserve">HC lines: deal crosswalk + exposure materiality</t>
@@ -1528,7 +1591,7 @@
     <t xml:space="preserve">CP: 125,097 rows / 4,604 lines / line_eq_cpcode=125,097 (ALL equal). HC: 338,140 rows / 714 lines / line_eq_cpcode=0 (NONE equal).</t>
   </si>
   <si>
-    <t xml:space="preserve">CONFIRMS the agent/fund structure — and the data proves it textually: a sample HC line CP maps to counterparty_long_name "VANGUARD GROUP INC (THE) AS AGENT FOR SELECT FUNDS". So: (1) CP-format deal lines ARE the counterparty (line=counterparty_code, 4,604 lines — the entity trades as/for itself, direct). (2) HC-format deal lines (714) are AGENT/FACILITY lines whose trades post to CP counterparties (one HC line -&gt; many CP codes, e.g. HC_(TDBK)_(LCH1) -&gt; CP L1US/L1GB). Facility_Line_Code = HC or CP; Counterparty_Line_Code = the CP code (always). For CP-format deal lines the two are equal; for HC they differ (crosswalk).</t>
+    <t xml:space="preserve">CONFIRMS the Holding Company structure — and the data proves it textually: a sample HC line CP maps to counterparty_long_name "VANGUARD GROUP INC (THE) AS AGENT FOR SELECT FUNDS". So: (1) CP-format deal lines ARE the counterparty (line=counterparty_code, 4,604 lines — the entity trades as/for itself, direct). (2) HC-format deal lines (714) are AGENT/FACILITY lines whose trades post to CP counterparties (one HC line -&gt; many CP codes, e.g. HC_(TDBK)_(LCH1) -&gt; CP L1US/L1GB). Facility_Line_Code = HC or CP; Counterparty_Line_Code = the CP code (always). For CP-format deal lines the two are equal; for HC they differ (crosswalk).</t>
   </si>
   <si>
     <t xml:space="preserve">HC lines fully attributed at line grain (no clients_report needed)</t>
@@ -1597,6 +1660,48 @@
     <t xml:space="preserve">ALL THREE FACTS RESOLVE CORRECTLY. Every Mosaic join verified with numbers: deal-&gt;line fact on Line (5,315); deal-&gt;CP dim on Counterparty_Code (8,508); line/scenario-&gt;CP dim on Line=counterparty_code (10,417); scenario-&gt;line fact ties exactly (0 mismatch); CP+HC disjoint (VJ-NODOUBLE=0, third independent confirmation of no double-count). Residuals all trivial/explained: 6 "Other" deal rows (malformed line), 3 drill misses, 107 CP lines absent from lines_report/exp_decomp, IA sparsity (data reality). MODEL IS SOUND. Pending only: data-owner sign-off on HC/CP terminology, scenario friendly-name labels (esp. "Product"=prod_max), IM definition.</t>
   </si>
   <si>
+    <t xml:space="preserve">Deal fact: null-line IM/cash stubs excluded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pfe_deals_report -&gt; vw_pfe_deals_by_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What were the 6 "Other"-class deal rows, and should they be in the deal fact?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT Line, Line_Class, Counterparty_Code, MTM, Years_To_Maturity, Deal_Id
+FROM vw_pfe_deals_by_line WHERE Line_Class = 'Other';</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 rows: line NULL, MTM NULL, Years_To_Maturity=50 (placeholder), book=TCIM_IM_book, Deal_Id like USD_CASH_...; only Counterparty_Code + Deal_Id populated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These are internal IM/CASH technical stubs (USD cash records in an IM book with a 50yr placeholder tenor), NOT counterparty deals-by-line — no line, no MTM, no exposure. EXCLUDED from the deal fact via base filter: line IS NOT NULL AND trim(line)&lt;&gt;''. Result: Line_Class is now only CP/HC (no 'Other'). NOTE: their no_line_indicator is NULL — the COALESCE(...,false)=false filter alone kept them; the line-not-null clause removes them. Same STRING/null-trap family as elsewhere: a plain '=false' filter does not exclude null-indicator rows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC = Holding Company (data-owner confirmed); immediate_parent mapping; HC exposure independent (not a rollup)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pfe_clients_report immediate_parent / ultimate_parent · pfe_ats_summary HC lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is HC, how do HC lines map to counterparties, and is HC exposure a rollup of its children (double-count)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-- HC lines vs immediate_parent (all match); HC exposure vs SUM(child CP-line exposure)
+WITH hc_exp AS (SELECT trim(upper(line)) hc_line, max_of_all hc_pfe FROM pfe_ats_summary WHERE line LIKE 'HC%'),
+ child_exp AS (SELECT trim(upper(cr.immediate_parent)) hc_line, SUM(a.max_of_all) children_pfe
+   FROM pfe_clients_report cr JOIN pfe_ats_summary a ON a.line=cr.counterparty_code
+   WHERE cr.immediate_parent LIKE 'HC%' GROUP BY 1)
+SELECT h.hc_pfe, c.children_pfe, h.hc_pfe-c.children_pfe diff FROM hc_exp h JOIN child_exp c ON h.hc_line=c.hc_line;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA OWNER: HC=Holding Company; ats_summary sources from lines_report (CP &amp; HC line types); use immediate_parent as the HC-level key. All 1,387 HC lines match an immediate_parent. Rollup test: hc_pfe vs children_pfe diff is LARGE and BOTH directions (HSBH hc=0/children=150m; MRLI hc=209m/children=0; APHB 414m/119m) — NOT equal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFIRMED: HC = Holding Company. Hierarchy in clients_report: counterparty_code (CP, leaf) -&gt; immediate_parent (HC) -&gt; ultimate_parent (UP). HC lines map to their counterparty family via immediate_parent (all 1,387 resolve). CRITICAL: HC exposure is INDEPENDENT of its children — NOT a rollup (rollup test diffs large/erratic both ways). So CP+HC are ADDITIVE, no double-count — a counterparty can trade on its OWN CP line AND its holding company has its OWN HC book; two separate exposures. The 4,992 CP/HC overlap is that legitimate case, NOT duplication. Confirmed twice now: (1) reporting-scope CP+HC=validated pack; (2) this rollup test. CP dim mapping is two-path: CP lines on Line=counterparty_code; HC lines on Line=immediate_parent (ATTRIBUTION, not aggregation).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Conform group</t>
   </si>
   <si>
@@ -1771,7 +1876,7 @@
     <t xml:space="preserve">clean (n-1)</t>
   </si>
   <si>
-    <t xml:space="preserve">KEY FINDING: the Line value in ats_summary/asts IS the counterparty_code in pfe_clients_report — same identifier. So the CP dimension relates to the line fact on Line = counterparty_code directly (NO c2c_line/cont_line unpivot, NO no_line_indicator logic). Confirmed exact: three-way join clients_report/asts/ats_summary on counterparty_code=Line gives 10,417 = 10,417 = 10,417 distinct. COVERAGE: 10,417 of 11,804 lines match; 1,387 lines have no counterparty_code in clients_report (LEFT relationship -&gt; null CP for those; logged as anomaly). | HC LINES: 1,387 of 11,804 lines are HC_ format (not counterparty_codes) — they show null CP on this direct join. The 712 HC lines that traded resolve to a CP via the DEAL-TABLE crosswalk (deal.line=HC -&gt; deal.counterparty_code=CP -&gt; clients_report); the other 675 are empty (immaterial). Optional: add a HC-&gt;CP bridge via pfe_deals_report if HC counterparty attribution is needed in the line/scenario facts. | HC lines (1,387) resolve NULL here (not in clients_report) but are FULLY self-attributed from ats_summary (industry/otc_sft/rating all 0 nulls) — sliceable without the CP dim. Not forced into clients_report (HC-&gt;CP is one-to-many). Deep CP detail for HC reached at deal grain.</t>
+    <t xml:space="preserve">KEY FINDING: the Line value in ats_summary/asts IS the counterparty_code in pfe_clients_report — same identifier. So the CP dimension relates to the line fact on Line = counterparty_code directly (NO c2c_line/cont_line unpivot, NO no_line_indicator logic). Confirmed exact: three-way join clients_report/asts/ats_summary on counterparty_code=Line gives 10,417 = 10,417 = 10,417 distinct. COVERAGE: 10,417 of 11,804 lines match; 1,387 lines have no counterparty_code in clients_report (LEFT relationship -&gt; null CP for those; logged as anomaly). | HC LINES: 1,387 of 11,804 lines are HC_ format (not counterparty_codes) — they show null CP on this direct join. The 712 HC lines that traded resolve to a CP via the DEAL-TABLE crosswalk (deal.line=HC -&gt; deal.counterparty_code=CP -&gt; clients_report); the other 675 are empty (immaterial). Optional: add a HC-&gt;CP bridge via pfe_deals_report if HC counterparty attribution is needed in the line/scenario facts. | HC lines (1,387) resolve NULL here (not in clients_report) but are FULLY self-attributed from ats_summary (industry/otc_sft/rating all 0 nulls) — sliceable without the CP dim. Not forced into clients_report (HC-&gt;CP is one-to-many). Deep CP detail for HC reached at deal grain. | Dimension is now vw_dim_client (self-sufficient, one row per counterparty). v1: CP lines join on Line=Counterparty_Code. HC lines map via Immediate_Parent (=Holding Company) — carried but DEFERRED (v1 HC drill uses the deal fact).</t>
   </si>
   <si>
     <t xml:space="preserve">dim_scenario</t>
@@ -1804,19 +1909,19 @@
     <t xml:space="preserve">Many line-scenario rows to one scenario.</t>
   </si>
   <si>
-    <t xml:space="preserve">Same key as the line fact: Line = counterparty_code (Line IS the counterparty_code). Relate the scenario fact to the CP dimension on Line, NOT on Counterparty_Name (name is display-only). Same 1,387 lines fall out (no counterparty_code in clients_report).</t>
+    <t xml:space="preserve">Same key as the line fact: Line = counterparty_code (Line IS the counterparty_code). Relate the scenario fact to the CP dimension on Line, NOT on Counterparty_Name (name is display-only). Same 1,387 lines fall out (no counterparty_code in clients_report). | Dimension is now vw_dim_client (self-sufficient, one row per counterparty). v1: CP lines join on Line=Counterparty_Code. HC lines map via Immediate_Parent (=Holding Company) — carried but DEFERRED (v1 HC drill uses the deal fact).</t>
   </si>
   <si>
     <t xml:space="preserve">Line = Line (deal.line = line-fact line)</t>
   </si>
   <si>
-    <t xml:space="preserve">EXPOSURE DRILL: deal.line is the UNIFIED HC/CP exposure key (CP where line=counterparty_code, HC where it is a facility) — matches the line fact 1:1 (4,603 CP + 712 HC = 5,315, no double-count). Deal relates to the line fact on LINE, NOT on counterparty_code. (counterparty_code is the CP-attribution key -&gt; CP dimension, a separate relationship.)</t>
+    <t xml:space="preserve">EXPOSURE DRILL: deal.line is the UNIFIED HC/CP exposure key (CP where line=counterparty_code, HC where it is a facility) — matches the line fact 1:1 (4,603 CP + 712 HC = 5,315, no double-count). Deal relates to the line fact on LINE, NOT on counterparty_code. (counterparty_code is the CP-attribution key -&gt; CP dimension, a separate relationship.) | NOTE: this relationship is now defined ONLY in the Mosaic model — the SQL LEFT JOIN was removed from the deal view so the views stay decoupled. Relate on Line = Line.</t>
   </si>
   <si>
     <t xml:space="preserve">Counterparty_Code = counterparty_code</t>
   </si>
   <si>
-    <t xml:space="preserve">CP ATTRIBUTION: deal.counterparty_code (always CP format) -&gt; clients_report.counterparty_code. This is the counterparty the trade posts to. counterparty_long_name in deals tracks the CP code (varies by CP), so it is the COUNTERPARTY name, not the facility name.</t>
+    <t xml:space="preserve">CP ATTRIBUTION: deal.counterparty_code (always CP format) -&gt; clients_report.counterparty_code. This is the counterparty the trade posts to. counterparty_long_name in deals tracks the CP code (varies by CP), so it is the COUNTERPARTY name, not the facility name. | Dimension is now vw_dim_client (self-sufficient, one row per counterparty). v1: CP lines join on Line=Counterparty_Code. HC lines map via Immediate_Parent (=Holding Company) — carried but DEFERRED (v1 HC drill uses the deal fact).</t>
   </si>
   <si>
     <t xml:space="preserve">vw_pfe_asts_scenario  &lt;-&gt;  vw_pfe_ats_lines_detail</t>
@@ -2677,7 +2782,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -3271,6 +3376,56 @@
       </c>
       <c r="L16" s="6"/>
     </row>
+    <row r="17" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3287,7 +3442,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
@@ -3312,90 +3467,90 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>90</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>50</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>92</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
@@ -3405,36 +3560,36 @@
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
       <c r="R2" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>50</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
@@ -3445,30 +3600,30 @@
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>50</v>
@@ -3483,30 +3638,30 @@
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
       <c r="R4" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>50</v>
@@ -3521,30 +3676,30 @@
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
       <c r="R5" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>50</v>
@@ -3559,30 +3714,30 @@
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>50</v>
@@ -3597,30 +3752,30 @@
       <c r="P7" s="10"/>
       <c r="Q7" s="10"/>
       <c r="R7" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>50</v>
@@ -3635,30 +3790,30 @@
       <c r="P8" s="10"/>
       <c r="Q8" s="10"/>
       <c r="R8" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>50</v>
@@ -3666,43 +3821,43 @@
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
       <c r="O9" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P9" s="10"/>
       <c r="Q9" s="10"/>
       <c r="R9" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>50</v>
@@ -3710,43 +3865,43 @@
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
       <c r="O10" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P10" s="10"/>
       <c r="Q10" s="10"/>
       <c r="R10" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>50</v>
@@ -3754,43 +3909,43 @@
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
       <c r="O11" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P11" s="10"/>
       <c r="Q11" s="10"/>
       <c r="R11" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>50</v>
@@ -3798,49 +3953,49 @@
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="R12" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>50</v>
@@ -3855,30 +4010,30 @@
       <c r="P13" s="10"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>50</v>
@@ -3893,30 +4048,30 @@
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
       <c r="R14" s="11" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>50</v>
@@ -3924,43 +4079,43 @@
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
       <c r="O15" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P15" s="10"/>
       <c r="Q15" s="10"/>
       <c r="R15" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>50</v>
@@ -3968,43 +4123,43 @@
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
       <c r="K16" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="O16" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>50</v>
@@ -4012,43 +4167,43 @@
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
       <c r="O17" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>50</v>
@@ -4056,43 +4211,43 @@
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
       <c r="O18" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P18" s="10"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>50</v>
@@ -4107,30 +4262,30 @@
       <c r="P19" s="10"/>
       <c r="Q19" s="10"/>
       <c r="R19" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>50</v>
@@ -4138,47 +4293,47 @@
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P20" s="10"/>
       <c r="Q20" s="10"/>
       <c r="R20" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>50</v>
@@ -4186,47 +4341,47 @@
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P21" s="10"/>
       <c r="Q21" s="10"/>
       <c r="R21" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H22" s="10" t="s">
         <v>50</v>
@@ -4234,47 +4389,47 @@
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="10"/>
       <c r="R22" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H23" s="10" t="s">
         <v>50</v>
@@ -4282,47 +4437,47 @@
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P23" s="10"/>
       <c r="Q23" s="10"/>
       <c r="R23" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H24" s="10" t="s">
         <v>50</v>
@@ -4330,47 +4485,47 @@
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="O24" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P24" s="10"/>
       <c r="Q24" s="10"/>
       <c r="R24" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H25" s="10" t="s">
         <v>50</v>
@@ -4378,47 +4533,47 @@
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P25" s="10"/>
       <c r="Q25" s="10"/>
       <c r="R25" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>50</v>
@@ -4426,47 +4581,47 @@
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="O26" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P26" s="10"/>
       <c r="Q26" s="10"/>
       <c r="R26" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>50</v>
@@ -4474,53 +4629,53 @@
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P27" s="10"/>
       <c r="Q27" s="10"/>
       <c r="R27" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>50</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>92</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
@@ -4531,39 +4686,39 @@
       <c r="P28" s="10"/>
       <c r="Q28" s="10"/>
       <c r="R28" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>55</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>50</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H29" s="10" t="s">
         <v>92</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
@@ -4573,30 +4728,30 @@
       <c r="P29" s="10"/>
       <c r="Q29" s="10"/>
       <c r="R29" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>50</v>
@@ -4604,43 +4759,43 @@
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
       <c r="K30" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
       <c r="O30" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P30" s="10"/>
       <c r="Q30" s="10"/>
       <c r="R30" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>50</v>
@@ -4648,45 +4803,45 @@
       <c r="I31" s="10"/>
       <c r="J31" s="10"/>
       <c r="K31" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="P31" s="10"/>
       <c r="Q31" s="10"/>
       <c r="R31" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>50</v>
@@ -4694,47 +4849,47 @@
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
       <c r="K32" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="O32" s="10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="P32" s="10" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="Q32" s="10"/>
       <c r="R32" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>50</v>
@@ -4742,45 +4897,45 @@
       <c r="I33" s="10"/>
       <c r="J33" s="10"/>
       <c r="K33" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="P33" s="10"/>
       <c r="Q33" s="10"/>
       <c r="R33" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>50</v>
@@ -4788,45 +4943,45 @@
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="O34" s="10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="P34" s="10"/>
       <c r="Q34" s="10"/>
       <c r="R34" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>50</v>
@@ -4841,30 +4996,30 @@
       <c r="P35" s="10"/>
       <c r="Q35" s="10"/>
       <c r="R35" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>53</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>50</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>50</v>
@@ -4879,30 +5034,30 @@
       <c r="P36" s="10"/>
       <c r="Q36" s="10"/>
       <c r="R36" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>50</v>
@@ -4910,43 +5065,43 @@
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10"/>
       <c r="O37" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P37" s="10"/>
       <c r="Q37" s="10"/>
       <c r="R37" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>50</v>
@@ -4954,43 +5109,43 @@
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
       <c r="O38" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P38" s="10"/>
       <c r="Q38" s="10"/>
       <c r="R38" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>50</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>50</v>
@@ -5005,30 +5160,30 @@
       <c r="P39" s="10"/>
       <c r="Q39" s="10"/>
       <c r="R39" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>289</v>
+        <v>130</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>50</v>
@@ -5043,30 +5198,30 @@
       <c r="P40" s="10"/>
       <c r="Q40" s="10"/>
       <c r="R40" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>50</v>
@@ -5081,30 +5236,30 @@
       <c r="P41" s="10"/>
       <c r="Q41" s="10"/>
       <c r="R41" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H42" s="10" t="s">
         <v>50</v>
@@ -5119,30 +5274,30 @@
       <c r="P42" s="10"/>
       <c r="Q42" s="10"/>
       <c r="R42" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>50</v>
@@ -5157,36 +5312,36 @@
       <c r="P43" s="10"/>
       <c r="Q43" s="10"/>
       <c r="R43" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>45</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>50</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H44" s="10" t="s">
         <v>92</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
@@ -5197,30 +5352,30 @@
       <c r="P44" s="10"/>
       <c r="Q44" s="10"/>
       <c r="R44" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H45" s="10" t="s">
         <v>50</v>
@@ -5228,45 +5383,45 @@
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L45" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="P45" s="10"/>
       <c r="Q45" s="10"/>
       <c r="R45" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H46" s="10" t="s">
         <v>50</v>
@@ -5274,45 +5429,45 @@
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L46" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O46" s="10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="P46" s="10"/>
       <c r="Q46" s="10"/>
       <c r="R46" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>50</v>
@@ -5320,45 +5475,45 @@
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
       <c r="K47" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="P47" s="10"/>
       <c r="Q47" s="10"/>
       <c r="R47" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H48" s="10" t="s">
         <v>50</v>
@@ -5366,54 +5521,54 @@
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
       <c r="K48" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L48" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O48" s="10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="P48" s="10"/>
       <c r="Q48" s="10"/>
       <c r="R48" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>90</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>50</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>92</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
@@ -5423,39 +5578,39 @@
       <c r="P49" s="10"/>
       <c r="Q49" s="10"/>
       <c r="R49" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>289</v>
+        <v>130</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>50</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>92</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
@@ -5465,30 +5620,30 @@
       <c r="P50" s="10"/>
       <c r="Q50" s="10"/>
       <c r="R50" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H51" s="10" t="s">
         <v>50</v>
@@ -5496,53 +5651,53 @@
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
       <c r="K51" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="L51" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M51" s="10" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P51" s="10"/>
       <c r="Q51" s="10"/>
       <c r="R51" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H52" s="10" t="s">
         <v>50</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
@@ -5553,30 +5708,30 @@
       <c r="P52" s="10"/>
       <c r="Q52" s="10"/>
       <c r="R52" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>50</v>
@@ -5591,30 +5746,30 @@
       <c r="P53" s="10"/>
       <c r="Q53" s="10"/>
       <c r="R53" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>50</v>
@@ -5629,30 +5784,30 @@
       <c r="P54" s="10"/>
       <c r="Q54" s="10"/>
       <c r="R54" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H55" s="10" t="s">
         <v>50</v>
@@ -5667,30 +5822,30 @@
       <c r="P55" s="10"/>
       <c r="Q55" s="10"/>
       <c r="R55" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H56" s="10" t="s">
         <v>50</v>
@@ -5705,30 +5860,30 @@
       <c r="P56" s="10"/>
       <c r="Q56" s="10"/>
       <c r="R56" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H57" s="10" t="s">
         <v>50</v>
@@ -5743,30 +5898,30 @@
       <c r="P57" s="10"/>
       <c r="Q57" s="10"/>
       <c r="R57" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>50</v>
@@ -5774,45 +5929,45 @@
       <c r="I58" s="10"/>
       <c r="J58" s="10"/>
       <c r="K58" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L58" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="O58" s="10" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="P58" s="10"/>
       <c r="Q58" s="10"/>
       <c r="R58" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>92</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>50</v>
@@ -5827,7 +5982,131 @@
       <c r="P59" s="10"/>
       <c r="Q59" s="10"/>
       <c r="R59" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -5860,217 +6139,217 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
@@ -6097,7 +6376,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -6111,25 +6390,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6137,22 +6416,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6160,22 +6439,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6183,22 +6462,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6206,22 +6485,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6229,22 +6508,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6252,22 +6531,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6275,22 +6554,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6298,22 +6577,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6321,22 +6600,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6344,22 +6623,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="129.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6367,22 +6646,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="129.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6390,22 +6669,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6413,22 +6692,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>470</v>
+        <v>491</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="139.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6436,22 +6715,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6459,22 +6738,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6482,22 +6761,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6505,22 +6784,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="159.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6528,22 +6807,68 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>504</v>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>527</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="174.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>532</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -6575,22 +6900,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>505</v>
+        <v>538</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>506</v>
+        <v>539</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>507</v>
+        <v>540</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>508</v>
+        <v>541</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>509</v>
+        <v>542</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>510</v>
+        <v>543</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6598,229 +6923,229 @@
         <v>90</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>511</v>
+        <v>544</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>512</v>
+        <v>545</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>513</v>
+        <v>546</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>514</v>
+        <v>547</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>515</v>
+        <v>548</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>516</v>
+        <v>549</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>517</v>
+        <v>550</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>518</v>
+        <v>551</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>519</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>520</v>
+        <v>553</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>521</v>
+        <v>554</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>522</v>
+        <v>555</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>523</v>
+        <v>556</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>524</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>525</v>
+        <v>558</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>526</v>
+        <v>559</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>513</v>
+        <v>546</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>527</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>528</v>
+        <v>561</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>529</v>
+        <v>562</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>530</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>531</v>
+        <v>564</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>529</v>
+        <v>562</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>532</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>533</v>
+        <v>566</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>529</v>
+        <v>562</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>534</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>535</v>
+        <v>568</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>529</v>
+        <v>562</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>536</v>
+        <v>569</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>538</v>
+        <v>571</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>539</v>
+        <v>572</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>540</v>
+        <v>573</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>541</v>
+        <v>574</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>542</v>
+        <v>575</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>543</v>
+        <v>576</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>544</v>
+        <v>577</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>545</v>
+        <v>578</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>546</v>
+        <v>579</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>547</v>
+        <v>580</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>548</v>
+        <v>581</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>549</v>
+        <v>582</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>529</v>
+        <v>562</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>550</v>
+        <v>583</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>551</v>
+        <v>584</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>552</v>
+        <v>585</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -6860,202 +7185,202 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>553</v>
+        <v>586</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>554</v>
+        <v>587</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>555</v>
+        <v>588</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>556</v>
+        <v>589</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>557</v>
+        <v>590</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>559</v>
+        <v>592</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>560</v>
+        <v>593</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>561</v>
+        <v>594</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>562</v>
+        <v>595</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>563</v>
+        <v>596</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>564</v>
+        <v>597</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>565</v>
+        <v>598</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>561</v>
+        <v>594</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>566</v>
+        <v>599</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>567</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>568</v>
+        <v>601</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>569</v>
+        <v>602</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>570</v>
+        <v>603</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>566</v>
+        <v>599</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>571</v>
+        <v>604</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>564</v>
+        <v>597</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>572</v>
+        <v>605</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>561</v>
+        <v>594</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>566</v>
+        <v>599</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>573</v>
+        <v>606</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>560</v>
+        <v>593</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>561</v>
+        <v>594</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>562</v>
+        <v>595</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>574</v>
+        <v>607</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>568</v>
+        <v>601</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>575</v>
+        <v>608</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>570</v>
+        <v>603</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>566</v>
+        <v>599</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>576</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>577</v>
+        <v>610</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>561</v>
+        <v>594</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>566</v>
+        <v>599</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>578</v>
+        <v>611</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>579</v>
+        <v>612</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>580</v>
+        <v>613</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>581</v>
+        <v>614</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>582</v>
+        <v>615</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>583</v>
+        <v>616</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>584</v>
+        <v>617</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>585</v>
+        <v>618</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>580</v>
+        <v>613</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>581</v>
+        <v>614</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>582</v>
+        <v>615</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>583</v>
+        <v>616</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>586</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -7088,317 +7413,317 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>587</v>
+        <v>620</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>588</v>
+        <v>621</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>589</v>
+        <v>622</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>590</v>
+        <v>623</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>591</v>
+        <v>624</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>592</v>
+        <v>625</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>593</v>
+        <v>626</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>594</v>
+        <v>627</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>594</v>
+        <v>627</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="G3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>594</v>
+        <v>627</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>597</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>598</v>
+        <v>631</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>599</v>
+        <v>632</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>600</v>
+        <v>633</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>601</v>
+        <v>634</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>594</v>
+        <v>627</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="G6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>594</v>
+        <v>627</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="G7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>594</v>
+        <v>627</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="G8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>594</v>
+        <v>627</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="G9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>602</v>
+        <v>635</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>603</v>
+        <v>636</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>604</v>
+        <v>637</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>605</v>
+        <v>638</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>606</v>
+        <v>639</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>316</v>
-      </c>
       <c r="C11" s="10" t="s">
-        <v>607</v>
+        <v>640</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>608</v>
+        <v>641</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>609</v>
+        <v>642</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>610</v>
+        <v>643</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>611</v>
+        <v>644</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>594</v>
+        <v>627</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>612</v>
+        <v>645</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>613</v>
+        <v>646</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>600</v>
+        <v>633</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>614</v>
+        <v>647</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>598</v>
+        <v>631</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>600</v>
+        <v>633</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>615</v>
+        <v>648</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>616</v>
+        <v>649</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>600</v>
+        <v>633</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>617</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -7429,53 +7754,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>618</v>
+        <v>651</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>619</v>
+        <v>652</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>620</v>
+        <v>653</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>621</v>
+        <v>654</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>593</v>
+        <v>626</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>45</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>622</v>
+        <v>655</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>623</v>
+        <v>656</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>624</v>
+        <v>657</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>625</v>
+        <v>658</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>117</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>626</v>
+        <v>659</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>627</v>
+        <v>660</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>628</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
